--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/region-de-antofagasta.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/region-de-antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4291-1152-CM26</t>
+          <t>4291-24-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>16867.36</v>
+        <v>44125.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2384-148-CM26</t>
+          <t>4291-83-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2934.54</v>
+        <v>10347.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1158-106-CM26</t>
+          <t>3149-78-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4823.01</v>
+        <v>26700.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>947750-31-CM26</t>
+          <t>3834-48-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -745,39 +745,35 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>184010.89</v>
+        <v>5625.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1233623-521-CM26</t>
+          <t>3858-61-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -787,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -802,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -817,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6218.23</v>
+        <v>8522.780000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1233623-579-CM26</t>
+          <t>4051-74-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -863,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -878,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>70768.14999999999</v>
+        <v>8094.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1375735-41-CM26</t>
+          <t>1375735-11-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -924,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -939,6 +935,3426 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
+        <v>45410.16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4468-72-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.253.200-7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>2941.68</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4468-73-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.253.200-7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>2941.68</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2429-1808-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>44561.57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4291-542-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>3130.91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4468-93-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.253.200-7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>3777.06</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2385-355-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>31166.09</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4291-672-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>24675.36</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3917-148-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.020.500-9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>26030.83</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3916-271-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.020.500-9</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ESPEX INGENIERIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>7015.05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3053-20-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>21123.64</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3053-21-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-06-09</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>19246.92</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>881-200-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>72.224.100-2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>15628.27</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>881-201-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>72.224.100-2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>2873.85</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3917-188-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.020.500-9</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>30178.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3917-189-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.020.500-9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>14732.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3917-213-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.020.500-9</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>27274.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1230848-159-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>70.954.900-6</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>36125.51</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3858-284-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>17017</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3858-297-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>24273.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1233623-312-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>7378.48</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1233623-301-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>5121.76</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1233623-290-CM25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>4292.33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3858-322-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>7468.44</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3858-318-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>8513.799999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1233623-379-CM25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>10726.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1233623-376-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>COMPUTACION E INGENIERIA S A</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>96.693.120-5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>35756.64</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1233623-339-CM25</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>4914.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1233623-308-CM25</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>18468.56</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1233623-307-CM25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>8032.38</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1233623-306-CM25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>11523.96</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4291-1649-CM25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>15066.83</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3916-411-CM25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.020.500-9</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>5942.31</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2429-2507-CM25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>27569.92</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3858-396-CM25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>8091.17</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2429-2579-CM25</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>7754.04</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2429-2586-CM25</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>6030.92</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2429-2610-CM25</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>2584.68</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4291-1964-CM25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>3451</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4291-1992-CM25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>COMERCIAL FELP SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.427.199-8</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>3474.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4291-2009-CM25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>COMERCIAL FELP SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.427.199-8</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>2606.1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1233822-60-CM25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>65.076.481-1</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>5534.45</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2429-2675-CM25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>3398.16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1233623-813-CM25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>56721.06</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1233623-815-CM25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>58461.65</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4291-2240-CM25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>19634.74</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3845-65-CM25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.253.200-7</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>9518.83</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1261592-4302-CM25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>25454.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1261592-4301-CM25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TIC SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>5090.82</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1233623-897-CM25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-1-LR24</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>63308</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4291-1152-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>16867.36</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2384-148-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>2934.54</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1158-106-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>4823.01</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>947750-31-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ARTEC INVERSIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>184010.89</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1233623-521-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>6218.23</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1233623-579-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>70768.14999999999</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1375735-41-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.981.250-6</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
         <v>4569.6</v>
       </c>
     </row>
